--- a/Excel/EquipRedConfig.xlsx
+++ b/Excel/EquipRedConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="22">
   <si>
     <t>#</t>
   </si>
@@ -57,6 +57,9 @@
   </si>
   <si>
     <t>int</t>
+  </si>
+  <si>
+    <t>double</t>
   </si>
   <si>
     <t>生命倍率</t>
@@ -1129,7 +1132,7 @@
         <v>9</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="3:10">
@@ -1155,7 +1158,7 @@
         <v>10</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="3:10">
@@ -1181,7 +1184,7 @@
         <v>10</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="3:10">
@@ -1207,7 +1210,7 @@
         <v>5</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="3:10">
@@ -1233,7 +1236,7 @@
         <v>5</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="3:10">
@@ -1259,7 +1262,7 @@
         <v>5</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="3:10">
@@ -1285,7 +1288,7 @@
         <v>1</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="3:10">
@@ -1308,10 +1311,10 @@
         <v>1</v>
       </c>
       <c r="I12" s="1">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="3:10">
@@ -1337,7 +1340,7 @@
         <v>20</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="3:10">
@@ -1363,7 +1366,7 @@
         <v>1</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="3:10">
@@ -1389,7 +1392,7 @@
         <v>20</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="3:10">
@@ -1415,7 +1418,7 @@
         <v>30</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="3:10">
@@ -1441,7 +1444,7 @@
         <v>40</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="3:10">
@@ -1467,7 +1470,7 @@
         <v>20</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="3:10">
@@ -1493,7 +1496,7 @@
         <v>30</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="3:10">
@@ -1519,7 +1522,7 @@
         <v>40</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="3:10">
@@ -1545,7 +1548,7 @@
         <v>20</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="3:10">
@@ -1571,7 +1574,7 @@
         <v>30</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="3:10">
@@ -1597,7 +1600,7 @@
         <v>40</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/EquipRedConfig.xlsx
+++ b/Excel/EquipRedConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Excel/EquipRedConfig.xlsx
+++ b/Excel/EquipRedConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="25">
   <si>
     <t>#</t>
   </si>
@@ -93,6 +93,15 @@
   </si>
   <si>
     <t>道攻倍率</t>
+  </si>
+  <si>
+    <t>物伤倍率</t>
+  </si>
+  <si>
+    <t>韧性倍率</t>
+  </si>
+  <si>
+    <t>道伤倍率</t>
   </si>
 </sst>
 </file>
@@ -1050,7 +1059,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:J24"/>
+  <dimension ref="C1:J37"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -1603,6 +1612,318 @@
         <v>12</v>
       </c>
     </row>
+    <row r="26" spans="3:10">
+      <c r="C26" s="1">
+        <v>19</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
+      <c r="E26" s="1">
+        <v>8</v>
+      </c>
+      <c r="F26" s="1">
+        <v>2</v>
+      </c>
+      <c r="G26" s="1">
+        <v>2004</v>
+      </c>
+      <c r="H26" s="1">
+        <v>20</v>
+      </c>
+      <c r="I26" s="1">
+        <v>20</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="3:10">
+      <c r="C27" s="1">
+        <v>20</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
+      <c r="E27" s="1">
+        <v>8</v>
+      </c>
+      <c r="F27" s="1">
+        <v>6</v>
+      </c>
+      <c r="G27" s="1">
+        <v>2007</v>
+      </c>
+      <c r="H27" s="1">
+        <v>30</v>
+      </c>
+      <c r="I27" s="1">
+        <v>30</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="3:10">
+      <c r="C28" s="1">
+        <v>21</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
+      <c r="E28" s="1">
+        <v>8</v>
+      </c>
+      <c r="F28" s="1">
+        <v>8</v>
+      </c>
+      <c r="G28" s="1">
+        <v>2002</v>
+      </c>
+      <c r="H28" s="1">
+        <v>40</v>
+      </c>
+      <c r="I28" s="1">
+        <v>40</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="3:10">
+      <c r="C29" s="1">
+        <v>22</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
+      <c r="E29" s="1">
+        <v>8</v>
+      </c>
+      <c r="F29" s="1">
+        <v>10</v>
+      </c>
+      <c r="G29" s="1">
+        <v>2012</v>
+      </c>
+      <c r="H29" s="1">
+        <v>40</v>
+      </c>
+      <c r="I29" s="1">
+        <v>40</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="30" spans="3:10">
+      <c r="C30" s="1">
+        <v>23</v>
+      </c>
+      <c r="D30" s="1">
+        <v>2</v>
+      </c>
+      <c r="E30" s="1">
+        <v>8</v>
+      </c>
+      <c r="F30" s="1">
+        <v>2</v>
+      </c>
+      <c r="G30" s="1">
+        <v>2005</v>
+      </c>
+      <c r="H30" s="1">
+        <v>20</v>
+      </c>
+      <c r="I30" s="1">
+        <v>20</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="3:10">
+      <c r="C31" s="1">
+        <v>24</v>
+      </c>
+      <c r="D31" s="1">
+        <v>2</v>
+      </c>
+      <c r="E31" s="1">
+        <v>8</v>
+      </c>
+      <c r="F31" s="1">
+        <v>6</v>
+      </c>
+      <c r="G31" s="1">
+        <v>2008</v>
+      </c>
+      <c r="H31" s="1">
+        <v>30</v>
+      </c>
+      <c r="I31" s="1">
+        <v>30</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="3:10">
+      <c r="C32" s="1">
+        <v>25</v>
+      </c>
+      <c r="D32" s="1">
+        <v>2</v>
+      </c>
+      <c r="E32" s="1">
+        <v>8</v>
+      </c>
+      <c r="F32" s="1">
+        <v>8</v>
+      </c>
+      <c r="G32" s="1">
+        <v>2001</v>
+      </c>
+      <c r="H32" s="1">
+        <v>40</v>
+      </c>
+      <c r="I32" s="1">
+        <v>40</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="3:10">
+      <c r="C33" s="1">
+        <v>26</v>
+      </c>
+      <c r="D33" s="1">
+        <v>2</v>
+      </c>
+      <c r="E33" s="1">
+        <v>8</v>
+      </c>
+      <c r="F33" s="1">
+        <v>10</v>
+      </c>
+      <c r="G33" s="1">
+        <v>2012</v>
+      </c>
+      <c r="H33" s="1">
+        <v>40</v>
+      </c>
+      <c r="I33" s="1">
+        <v>40</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="34" spans="3:10">
+      <c r="C34" s="1">
+        <v>27</v>
+      </c>
+      <c r="D34" s="1">
+        <v>3</v>
+      </c>
+      <c r="E34" s="1">
+        <v>8</v>
+      </c>
+      <c r="F34" s="1">
+        <v>2</v>
+      </c>
+      <c r="G34" s="1">
+        <v>2006</v>
+      </c>
+      <c r="H34" s="1">
+        <v>20</v>
+      </c>
+      <c r="I34" s="1">
+        <v>20</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35" spans="3:10">
+      <c r="C35" s="1">
+        <v>28</v>
+      </c>
+      <c r="D35" s="1">
+        <v>3</v>
+      </c>
+      <c r="E35" s="1">
+        <v>8</v>
+      </c>
+      <c r="F35" s="1">
+        <v>6</v>
+      </c>
+      <c r="G35" s="1">
+        <v>2009</v>
+      </c>
+      <c r="H35" s="1">
+        <v>30</v>
+      </c>
+      <c r="I35" s="1">
+        <v>30</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="36" spans="3:10">
+      <c r="C36" s="1">
+        <v>29</v>
+      </c>
+      <c r="D36" s="1">
+        <v>3</v>
+      </c>
+      <c r="E36" s="1">
+        <v>8</v>
+      </c>
+      <c r="F36" s="1">
+        <v>8</v>
+      </c>
+      <c r="G36" s="1">
+        <v>2002</v>
+      </c>
+      <c r="H36" s="1">
+        <v>40</v>
+      </c>
+      <c r="I36" s="1">
+        <v>40</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" spans="3:10">
+      <c r="C37" s="1">
+        <v>30</v>
+      </c>
+      <c r="D37" s="1">
+        <v>3</v>
+      </c>
+      <c r="E37" s="1">
+        <v>8</v>
+      </c>
+      <c r="F37" s="1">
+        <v>10</v>
+      </c>
+      <c r="G37" s="1">
+        <v>2012</v>
+      </c>
+      <c r="H37" s="1">
+        <v>40</v>
+      </c>
+      <c r="I37" s="1">
+        <v>40</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:C5" errorStyle="warning">

--- a/Excel/EquipRedConfig.xlsx
+++ b/Excel/EquipRedConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1060,7 +1060,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="C1:J37"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
     <col min="4" max="6" width="16.25" style="1" customWidth="1"/>
@@ -1075,7 +1075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="3:9">
+    <row r="3" ht="13.5" spans="3:9">
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
@@ -1098,7 +1098,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="3:9">
+    <row r="4" ht="13.5" spans="3:9">
       <c r="C4" s="2" t="s">
         <v>8</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="3:9">
+    <row r="5" ht="13.5" spans="3:9">
       <c r="C5" s="2" t="s">
         <v>9</v>
       </c>
@@ -1629,10 +1629,10 @@
         <v>2004</v>
       </c>
       <c r="H26" s="1">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="I26" s="1">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="J26" s="1" t="s">
         <v>20</v>
@@ -1655,10 +1655,10 @@
         <v>2007</v>
       </c>
       <c r="H27" s="1">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I27" s="1">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="J27" s="1" t="s">
         <v>22</v>
@@ -1681,10 +1681,10 @@
         <v>2002</v>
       </c>
       <c r="H28" s="1">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="I28" s="1">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="J28" s="1" t="s">
         <v>11</v>
@@ -1733,10 +1733,10 @@
         <v>2005</v>
       </c>
       <c r="H30" s="1">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="I30" s="1">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="J30" s="1" t="s">
         <v>15</v>
@@ -1759,10 +1759,10 @@
         <v>2008</v>
       </c>
       <c r="H31" s="1">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I31" s="1">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="J31" s="1" t="s">
         <v>14</v>
@@ -1785,10 +1785,10 @@
         <v>2001</v>
       </c>
       <c r="H32" s="1">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="I32" s="1">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="J32" s="1" t="s">
         <v>11</v>
@@ -1837,10 +1837,10 @@
         <v>2006</v>
       </c>
       <c r="H34" s="1">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="I34" s="1">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="J34" s="1" t="s">
         <v>21</v>
@@ -1863,10 +1863,10 @@
         <v>2009</v>
       </c>
       <c r="H35" s="1">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I35" s="1">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="J35" s="1" t="s">
         <v>24</v>
@@ -1889,10 +1889,10 @@
         <v>2002</v>
       </c>
       <c r="H36" s="1">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="I36" s="1">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="J36" s="1" t="s">
         <v>11</v>

--- a/Excel/EquipRedConfig.xlsx
+++ b/Excel/EquipRedConfig.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="25">
   <si>
     <t>#</t>
   </si>
@@ -1059,7 +1059,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:J37"/>
+  <dimension ref="C1:J50"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -1924,6 +1924,318 @@
         <v>23</v>
       </c>
     </row>
+    <row r="39" spans="3:10">
+      <c r="C39" s="1">
+        <v>31</v>
+      </c>
+      <c r="D39" s="1">
+        <v>1</v>
+      </c>
+      <c r="E39" s="1">
+        <v>9</v>
+      </c>
+      <c r="F39" s="1">
+        <v>2</v>
+      </c>
+      <c r="G39" s="1">
+        <v>2004</v>
+      </c>
+      <c r="H39" s="1">
+        <v>60</v>
+      </c>
+      <c r="I39" s="1">
+        <v>60</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" spans="3:10">
+      <c r="C40" s="1">
+        <v>32</v>
+      </c>
+      <c r="D40" s="1">
+        <v>1</v>
+      </c>
+      <c r="E40" s="1">
+        <v>9</v>
+      </c>
+      <c r="F40" s="1">
+        <v>6</v>
+      </c>
+      <c r="G40" s="1">
+        <v>2007</v>
+      </c>
+      <c r="H40" s="1">
+        <v>90</v>
+      </c>
+      <c r="I40" s="1">
+        <v>90</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="41" spans="3:10">
+      <c r="C41" s="1">
+        <v>33</v>
+      </c>
+      <c r="D41" s="1">
+        <v>1</v>
+      </c>
+      <c r="E41" s="1">
+        <v>9</v>
+      </c>
+      <c r="F41" s="1">
+        <v>8</v>
+      </c>
+      <c r="G41" s="1">
+        <v>2002</v>
+      </c>
+      <c r="H41" s="1">
+        <v>120</v>
+      </c>
+      <c r="I41" s="1">
+        <v>120</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="3:10">
+      <c r="C42" s="1">
+        <v>34</v>
+      </c>
+      <c r="D42" s="1">
+        <v>1</v>
+      </c>
+      <c r="E42" s="1">
+        <v>9</v>
+      </c>
+      <c r="F42" s="1">
+        <v>10</v>
+      </c>
+      <c r="G42" s="1">
+        <v>2012</v>
+      </c>
+      <c r="H42" s="1">
+        <v>60</v>
+      </c>
+      <c r="I42" s="1">
+        <v>60</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="43" spans="3:10">
+      <c r="C43" s="1">
+        <v>35</v>
+      </c>
+      <c r="D43" s="1">
+        <v>2</v>
+      </c>
+      <c r="E43" s="1">
+        <v>9</v>
+      </c>
+      <c r="F43" s="1">
+        <v>2</v>
+      </c>
+      <c r="G43" s="1">
+        <v>2005</v>
+      </c>
+      <c r="H43" s="1">
+        <v>60</v>
+      </c>
+      <c r="I43" s="1">
+        <v>60</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44" spans="3:10">
+      <c r="C44" s="1">
+        <v>36</v>
+      </c>
+      <c r="D44" s="1">
+        <v>2</v>
+      </c>
+      <c r="E44" s="1">
+        <v>9</v>
+      </c>
+      <c r="F44" s="1">
+        <v>6</v>
+      </c>
+      <c r="G44" s="1">
+        <v>2008</v>
+      </c>
+      <c r="H44" s="1">
+        <v>90</v>
+      </c>
+      <c r="I44" s="1">
+        <v>90</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45" spans="3:10">
+      <c r="C45" s="1">
+        <v>37</v>
+      </c>
+      <c r="D45" s="1">
+        <v>2</v>
+      </c>
+      <c r="E45" s="1">
+        <v>9</v>
+      </c>
+      <c r="F45" s="1">
+        <v>8</v>
+      </c>
+      <c r="G45" s="1">
+        <v>2001</v>
+      </c>
+      <c r="H45" s="1">
+        <v>120</v>
+      </c>
+      <c r="I45" s="1">
+        <v>120</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="3:10">
+      <c r="C46" s="1">
+        <v>38</v>
+      </c>
+      <c r="D46" s="1">
+        <v>2</v>
+      </c>
+      <c r="E46" s="1">
+        <v>9</v>
+      </c>
+      <c r="F46" s="1">
+        <v>10</v>
+      </c>
+      <c r="G46" s="1">
+        <v>2012</v>
+      </c>
+      <c r="H46" s="1">
+        <v>60</v>
+      </c>
+      <c r="I46" s="1">
+        <v>60</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="47" spans="3:10">
+      <c r="C47" s="1">
+        <v>39</v>
+      </c>
+      <c r="D47" s="1">
+        <v>3</v>
+      </c>
+      <c r="E47" s="1">
+        <v>9</v>
+      </c>
+      <c r="F47" s="1">
+        <v>2</v>
+      </c>
+      <c r="G47" s="1">
+        <v>2006</v>
+      </c>
+      <c r="H47" s="1">
+        <v>60</v>
+      </c>
+      <c r="I47" s="1">
+        <v>60</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="48" spans="3:10">
+      <c r="C48" s="1">
+        <v>40</v>
+      </c>
+      <c r="D48" s="1">
+        <v>3</v>
+      </c>
+      <c r="E48" s="1">
+        <v>9</v>
+      </c>
+      <c r="F48" s="1">
+        <v>6</v>
+      </c>
+      <c r="G48" s="1">
+        <v>2009</v>
+      </c>
+      <c r="H48" s="1">
+        <v>90</v>
+      </c>
+      <c r="I48" s="1">
+        <v>90</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="49" spans="3:10">
+      <c r="C49" s="1">
+        <v>41</v>
+      </c>
+      <c r="D49" s="1">
+        <v>3</v>
+      </c>
+      <c r="E49" s="1">
+        <v>9</v>
+      </c>
+      <c r="F49" s="1">
+        <v>8</v>
+      </c>
+      <c r="G49" s="1">
+        <v>2002</v>
+      </c>
+      <c r="H49" s="1">
+        <v>120</v>
+      </c>
+      <c r="I49" s="1">
+        <v>120</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50" spans="3:10">
+      <c r="C50" s="1">
+        <v>42</v>
+      </c>
+      <c r="D50" s="1">
+        <v>3</v>
+      </c>
+      <c r="E50" s="1">
+        <v>9</v>
+      </c>
+      <c r="F50" s="1">
+        <v>10</v>
+      </c>
+      <c r="G50" s="1">
+        <v>2012</v>
+      </c>
+      <c r="H50" s="1">
+        <v>60</v>
+      </c>
+      <c r="I50" s="1">
+        <v>60</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:C5" errorStyle="warning">

--- a/Excel/EquipRedConfig.xlsx
+++ b/Excel/EquipRedConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="26">
   <si>
     <t>#</t>
   </si>
@@ -92,16 +92,19 @@
     <t>物攻倍率</t>
   </si>
   <si>
+    <t>物伤倍率</t>
+  </si>
+  <si>
     <t>道攻倍率</t>
   </si>
   <si>
-    <t>物伤倍率</t>
+    <t>道伤倍率</t>
+  </si>
+  <si>
+    <t>攻击倍率</t>
   </si>
   <si>
     <t>韧性倍率</t>
-  </si>
-  <si>
-    <t>道伤倍率</t>
   </si>
 </sst>
 </file>
@@ -1070,12 +1073,12 @@
     <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="10:10">
+    <row r="1" spans="3:10">
       <c r="J1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" ht="13.5" spans="3:9">
+    <row r="3" ht="13.5" spans="3:10">
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
@@ -1098,7 +1101,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" ht="13.5" spans="3:9">
+    <row r="4" ht="13.5" spans="3:10">
       <c r="C4" s="2" t="s">
         <v>8</v>
       </c>
@@ -1121,7 +1124,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" ht="13.5" spans="3:9">
+    <row r="5" ht="13.5" spans="3:10">
       <c r="C5" s="2" t="s">
         <v>9</v>
       </c>
@@ -1418,7 +1421,7 @@
         <v>6</v>
       </c>
       <c r="G17" s="1">
-        <v>2002</v>
+        <v>2007</v>
       </c>
       <c r="H17" s="1">
         <v>30</v>
@@ -1427,7 +1430,7 @@
         <v>30</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="3:10">
@@ -1453,7 +1456,7 @@
         <v>40</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="3:10">
@@ -1522,7 +1525,7 @@
         <v>10</v>
       </c>
       <c r="G21" s="1">
-        <v>2001</v>
+        <v>2003</v>
       </c>
       <c r="H21" s="1">
         <v>40</v>
@@ -1557,7 +1560,7 @@
         <v>20</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="3:10">
@@ -1574,7 +1577,7 @@
         <v>6</v>
       </c>
       <c r="G23" s="1">
-        <v>2002</v>
+        <v>2009</v>
       </c>
       <c r="H23" s="1">
         <v>30</v>
@@ -1583,7 +1586,7 @@
         <v>30</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="3:10">
@@ -1609,7 +1612,7 @@
         <v>40</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="3:10">
@@ -1661,7 +1664,7 @@
         <v>60</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="3:10">
@@ -1678,7 +1681,7 @@
         <v>8</v>
       </c>
       <c r="G28" s="1">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="H28" s="1">
         <v>80</v>
@@ -1687,7 +1690,7 @@
         <v>80</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="3:10">
@@ -1713,7 +1716,7 @@
         <v>40</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30" spans="3:10">
@@ -1791,7 +1794,7 @@
         <v>80</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33" spans="3:10">
@@ -1817,7 +1820,7 @@
         <v>40</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="34" spans="3:10">
@@ -1843,7 +1846,7 @@
         <v>40</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35" spans="3:10">
@@ -1869,7 +1872,7 @@
         <v>60</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="36" spans="3:10">
@@ -1886,7 +1889,7 @@
         <v>8</v>
       </c>
       <c r="G36" s="1">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="H36" s="1">
         <v>80</v>
@@ -1895,7 +1898,7 @@
         <v>80</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37" spans="3:10">
@@ -1921,7 +1924,7 @@
         <v>40</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="39" spans="3:10">
@@ -1973,7 +1976,7 @@
         <v>90</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="41" spans="3:10">
@@ -1990,7 +1993,7 @@
         <v>8</v>
       </c>
       <c r="G41" s="1">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="H41" s="1">
         <v>120</v>
@@ -1999,7 +2002,7 @@
         <v>120</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="42" spans="3:10">
@@ -2025,7 +2028,7 @@
         <v>60</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="43" spans="3:10">
@@ -2103,7 +2106,7 @@
         <v>120</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="46" spans="3:10">
@@ -2129,7 +2132,7 @@
         <v>60</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="47" spans="3:10">
@@ -2155,7 +2158,7 @@
         <v>60</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="48" spans="3:10">
@@ -2181,7 +2184,7 @@
         <v>90</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="49" spans="3:10">
@@ -2198,7 +2201,7 @@
         <v>8</v>
       </c>
       <c r="G49" s="1">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="H49" s="1">
         <v>120</v>
@@ -2207,7 +2210,7 @@
         <v>120</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="50" spans="3:10">
@@ -2233,7 +2236,7 @@
         <v>60</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/EquipRedConfig.xlsx
+++ b/Excel/EquipRedConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="27">
   <si>
     <t>#</t>
   </si>
@@ -105,6 +105,9 @@
   </si>
   <si>
     <t>韧性倍率</t>
+  </si>
+  <si>
+    <t>破韧倍率</t>
   </si>
 </sst>
 </file>
@@ -1062,7 +1065,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:J50"/>
+  <dimension ref="C1:J63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -2239,6 +2242,318 @@
         <v>25</v>
       </c>
     </row>
+    <row r="52" spans="3:10">
+      <c r="C52" s="1">
+        <v>43</v>
+      </c>
+      <c r="D52" s="1">
+        <v>1</v>
+      </c>
+      <c r="E52" s="1">
+        <v>10</v>
+      </c>
+      <c r="F52" s="1">
+        <v>2</v>
+      </c>
+      <c r="G52" s="1">
+        <v>2004</v>
+      </c>
+      <c r="H52" s="1">
+        <v>80</v>
+      </c>
+      <c r="I52" s="1">
+        <v>80</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="53" spans="3:10">
+      <c r="C53" s="1">
+        <v>44</v>
+      </c>
+      <c r="D53" s="1">
+        <v>1</v>
+      </c>
+      <c r="E53" s="1">
+        <v>10</v>
+      </c>
+      <c r="F53" s="1">
+        <v>6</v>
+      </c>
+      <c r="G53" s="1">
+        <v>2007</v>
+      </c>
+      <c r="H53" s="1">
+        <v>120</v>
+      </c>
+      <c r="I53" s="1">
+        <v>120</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="54" spans="3:10">
+      <c r="C54" s="1">
+        <v>45</v>
+      </c>
+      <c r="D54" s="1">
+        <v>1</v>
+      </c>
+      <c r="E54" s="1">
+        <v>10</v>
+      </c>
+      <c r="F54" s="1">
+        <v>8</v>
+      </c>
+      <c r="G54" s="1">
+        <v>2001</v>
+      </c>
+      <c r="H54" s="1">
+        <v>160</v>
+      </c>
+      <c r="I54" s="1">
+        <v>160</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="55" spans="3:10">
+      <c r="C55" s="1">
+        <v>46</v>
+      </c>
+      <c r="D55" s="1">
+        <v>1</v>
+      </c>
+      <c r="E55" s="1">
+        <v>10</v>
+      </c>
+      <c r="F55" s="1">
+        <v>10</v>
+      </c>
+      <c r="G55" s="1">
+        <v>2013</v>
+      </c>
+      <c r="H55" s="1">
+        <v>80</v>
+      </c>
+      <c r="I55" s="1">
+        <v>80</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="56" spans="3:10">
+      <c r="C56" s="1">
+        <v>47</v>
+      </c>
+      <c r="D56" s="1">
+        <v>2</v>
+      </c>
+      <c r="E56" s="1">
+        <v>10</v>
+      </c>
+      <c r="F56" s="1">
+        <v>2</v>
+      </c>
+      <c r="G56" s="1">
+        <v>2005</v>
+      </c>
+      <c r="H56" s="1">
+        <v>80</v>
+      </c>
+      <c r="I56" s="1">
+        <v>80</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57" spans="3:10">
+      <c r="C57" s="1">
+        <v>48</v>
+      </c>
+      <c r="D57" s="1">
+        <v>2</v>
+      </c>
+      <c r="E57" s="1">
+        <v>10</v>
+      </c>
+      <c r="F57" s="1">
+        <v>6</v>
+      </c>
+      <c r="G57" s="1">
+        <v>2008</v>
+      </c>
+      <c r="H57" s="1">
+        <v>120</v>
+      </c>
+      <c r="I57" s="1">
+        <v>120</v>
+      </c>
+      <c r="J57" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="58" spans="3:10">
+      <c r="C58" s="1">
+        <v>49</v>
+      </c>
+      <c r="D58" s="1">
+        <v>2</v>
+      </c>
+      <c r="E58" s="1">
+        <v>10</v>
+      </c>
+      <c r="F58" s="1">
+        <v>8</v>
+      </c>
+      <c r="G58" s="1">
+        <v>2001</v>
+      </c>
+      <c r="H58" s="1">
+        <v>160</v>
+      </c>
+      <c r="I58" s="1">
+        <v>160</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="59" spans="3:10">
+      <c r="C59" s="1">
+        <v>50</v>
+      </c>
+      <c r="D59" s="1">
+        <v>2</v>
+      </c>
+      <c r="E59" s="1">
+        <v>10</v>
+      </c>
+      <c r="F59" s="1">
+        <v>10</v>
+      </c>
+      <c r="G59" s="1">
+        <v>2013</v>
+      </c>
+      <c r="H59" s="1">
+        <v>80</v>
+      </c>
+      <c r="I59" s="1">
+        <v>80</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="60" spans="3:10">
+      <c r="C60" s="1">
+        <v>51</v>
+      </c>
+      <c r="D60" s="1">
+        <v>3</v>
+      </c>
+      <c r="E60" s="1">
+        <v>10</v>
+      </c>
+      <c r="F60" s="1">
+        <v>2</v>
+      </c>
+      <c r="G60" s="1">
+        <v>2006</v>
+      </c>
+      <c r="H60" s="1">
+        <v>80</v>
+      </c>
+      <c r="I60" s="1">
+        <v>80</v>
+      </c>
+      <c r="J60" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="61" spans="3:10">
+      <c r="C61" s="1">
+        <v>52</v>
+      </c>
+      <c r="D61" s="1">
+        <v>3</v>
+      </c>
+      <c r="E61" s="1">
+        <v>10</v>
+      </c>
+      <c r="F61" s="1">
+        <v>6</v>
+      </c>
+      <c r="G61" s="1">
+        <v>2009</v>
+      </c>
+      <c r="H61" s="1">
+        <v>120</v>
+      </c>
+      <c r="I61" s="1">
+        <v>120</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="62" spans="3:10">
+      <c r="C62" s="1">
+        <v>53</v>
+      </c>
+      <c r="D62" s="1">
+        <v>3</v>
+      </c>
+      <c r="E62" s="1">
+        <v>10</v>
+      </c>
+      <c r="F62" s="1">
+        <v>8</v>
+      </c>
+      <c r="G62" s="1">
+        <v>2001</v>
+      </c>
+      <c r="H62" s="1">
+        <v>160</v>
+      </c>
+      <c r="I62" s="1">
+        <v>160</v>
+      </c>
+      <c r="J62" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="63" spans="3:10">
+      <c r="C63" s="1">
+        <v>54</v>
+      </c>
+      <c r="D63" s="1">
+        <v>3</v>
+      </c>
+      <c r="E63" s="1">
+        <v>10</v>
+      </c>
+      <c r="F63" s="1">
+        <v>10</v>
+      </c>
+      <c r="G63" s="1">
+        <v>2013</v>
+      </c>
+      <c r="H63" s="1">
+        <v>80</v>
+      </c>
+      <c r="I63" s="1">
+        <v>80</v>
+      </c>
+      <c r="J63" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:C5" errorStyle="warning">
